--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-22</t>
   </si>
 </sst>
 </file>
@@ -542,6 +545,17 @@
         <v>0.0194050542329173</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.000366408896459364</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.0191418101667362</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-23</t>
   </si>
 </sst>
 </file>
@@ -556,6 +559,17 @@
         <v>0.0191418101667362</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.000438835422588869</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.0209483990459622</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-26</t>
   </si>
 </sst>
 </file>
@@ -570,6 +573,17 @@
         <v>0.0209483990459622</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.000425728204466522</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0206331821216826</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-27</t>
   </si>
 </sst>
 </file>
@@ -584,6 +587,17 @@
         <v>0.0206331821216826</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.000409382574472485</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.0202332047504216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-28</t>
   </si>
 </sst>
 </file>
@@ -598,6 +601,17 @@
         <v>0.0202332047504216</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0.000415199912097402</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.0203764548461552</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-29</t>
   </si>
 </sst>
 </file>
@@ -612,6 +615,17 @@
         <v>0.0203764548461552</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0.000401760474195772</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.0200439635350839</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/volatilidad_ewma.xlsx
+++ b/volatilidad_ewma.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve">fecha</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t xml:space="preserve">2026-10-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-30</t>
   </si>
 </sst>
 </file>
@@ -626,6 +629,17 @@
         <v>0.0200439635350839</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="n">
+        <v>0.000388646969623519</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0197141312165543</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
